--- a/output/pdf_financials_xlsx/VIBE.xlsx
+++ b/output/pdf_financials_xlsx/VIBE.xlsx
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>1.431301</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>1.030899</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.99317</v>
       </c>
     </row>
     <row r="71">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>1.431301</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>1.030899</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.99317</v>
       </c>
     </row>
     <row r="72">
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>7.851702</v>
+        <v>6.420401</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>9.537952000000001</v>
+        <v>8.507053000000001</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>11.600303</v>
+        <v>10.607133</v>
       </c>
     </row>
     <row r="76">
@@ -1705,20 +1705,14 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>1.326810678626154</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>-0.1975699770002949</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>-0.129995801055914</v>
       </c>
     </row>
     <row r="81">
@@ -3205,7 +3199,11 @@
           <t>Lease obligations 8</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3711,7 +3709,11 @@
           <t>Lease obligations 9</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>1.431301</v>
       </c>
@@ -4298,7 +4300,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>-0.178884</v>
       </c>
